--- a/AAII_Financials/Quarterly/ARMK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARMK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>ARMK</t>
   </si>
@@ -656,537 +656,549 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46024</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45933</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44925</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44652</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44288</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44197</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44106</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43917</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43826</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43644</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43553</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43462</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43371</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43189</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43098</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43007</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42734</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5057900</v>
+      </c>
+      <c r="E8" s="3">
         <v>4907300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4831500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5048500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4626500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4279300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4552100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4416900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4376100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4199900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4407800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4200300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4053100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3916200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3913700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4390500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4127400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3860500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3948300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3551300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2981200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2819700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2743800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2692200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2152300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3731600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4253600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3951200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4010800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4000000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4265300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3913600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3971600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3939300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3965100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3654100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3593300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3621600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3735400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3543800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4619500</v>
+      </c>
+      <c r="E9" s="3">
         <v>4476300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4415400</v>
       </c>
-      <c r="F9" s="3">
-        <v>3290400</v>
-      </c>
       <c r="G9" s="3">
-        <v>4256300</v>
+        <v>3303100</v>
       </c>
       <c r="H9" s="3">
+        <v>4240800</v>
+      </c>
+      <c r="I9" s="3">
         <v>3919100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4140100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2769500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4040900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3869200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4045100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2662900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3754500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3620700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3591800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3957500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3747800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3491200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3571000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3197200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2691100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2594200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2537500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2464300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2208000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3226700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3520600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3503300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3595000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3640000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3794400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3383800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3526300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3561500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3520100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3231100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3232400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3226200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3299300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3152300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>438400</v>
+      </c>
+      <c r="E10" s="3">
         <v>431000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>416200</v>
       </c>
-      <c r="F10" s="3">
-        <v>1758100</v>
-      </c>
       <c r="G10" s="3">
-        <v>370100</v>
+        <v>1745400</v>
       </c>
       <c r="H10" s="3">
+        <v>385600</v>
+      </c>
+      <c r="I10" s="3">
         <v>360200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>412000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1647400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>335200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>330800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>362700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1537400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>298500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>295500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>321900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>433000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>379600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>369300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>377300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>354100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>290100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>225500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>206300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>227900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-55700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>504900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>733000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>447900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>415800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>360000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>470900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>529800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>445300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>377800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>445000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>423000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>360900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>395400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>436100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>391500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1229,8 +1241,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1351,8 +1364,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1473,58 +1489,61 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>70500</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>57800</v>
       </c>
       <c r="H14" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-25400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>20000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>51400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-376000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1532,45 +1551,45 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>-4100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>55900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>198600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-157300</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1586,8 +1605,8 @@
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
@@ -1595,130 +1614,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E15" s="3">
         <v>132200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>126000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>124300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>121800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>117100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>112800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>108100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>109100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>105500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>102800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>101300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>103200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>102600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>131500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>133000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>132300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>135500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>138600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>136200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>137300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>138600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>151200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>148100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>148000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>147900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>145200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>148800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>147900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>150700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>152500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>156900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>152900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>133800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>130000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>126400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>125300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>126500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>125600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1758,252 +1783,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4834200</v>
+      </c>
+      <c r="E17" s="3">
         <v>4683000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4614000</v>
       </c>
-      <c r="F17" s="3">
-        <v>4779600</v>
-      </c>
       <c r="G17" s="3">
-        <v>4443900</v>
+        <v>4792300</v>
       </c>
       <c r="H17" s="3">
+        <v>4428400</v>
+      </c>
+      <c r="I17" s="3">
         <v>4104500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4323700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4198500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4214400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4040800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4220800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3933400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3920500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3790100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3762000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4192200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3979500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3718500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3808000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3418900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2967800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2814300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2764300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2786100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2479900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3829200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3999300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3745100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3821900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3877200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3892000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3631100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3784900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3802800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3746100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3436200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3438600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3430200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3491300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3353100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E18" s="3">
         <v>224300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>217500</v>
       </c>
-      <c r="F18" s="3">
-        <v>268900</v>
-      </c>
       <c r="G18" s="3">
-        <v>182600</v>
+        <v>256200</v>
       </c>
       <c r="H18" s="3">
+        <v>198100</v>
+      </c>
+      <c r="I18" s="3">
         <v>174800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>228400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>218500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>161700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>159100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>187000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>266900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>132500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>126100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>151700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>198300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>147900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>142000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>140300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>132400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-20500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-93900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-327600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-97600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>254300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>206100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>188900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>122800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>373300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>282500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>186700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>136500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>219000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>217900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>154700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>191400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>244100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>190700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2046,8 +2078,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2090,261 +2123,267 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-98600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-91500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-89700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-93100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-93000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>26200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-96300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-107900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-92900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-98500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-78300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-85600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-82300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-84200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-82900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-92500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-89800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-94100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-76300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-62600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-61500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-97600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-65700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-68500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>359800</v>
+      </c>
+      <c r="E21" s="3">
         <v>356500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>343500</v>
       </c>
-      <c r="F21" s="3">
-        <v>393200</v>
-      </c>
       <c r="G21" s="3">
-        <v>304400</v>
+        <v>380500</v>
       </c>
       <c r="H21" s="3">
+        <v>319900</v>
+      </c>
+      <c r="I21" s="3">
         <v>291800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>341600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>331200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>269800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>268200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>292500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>369600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>233800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>229200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>153300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>231200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>189400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>184600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>182700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>178000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>175800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>46400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-50500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-272400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-48200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>323900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>265700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>255400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>186600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>441100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>342400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>253800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>195200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>276600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>285200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>219600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>219100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>304900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>247800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E22" s="3">
         <v>82200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>81900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>112500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>86400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>89700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>75800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>106800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>81500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>86400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>114600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>140500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>112200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>113600</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
@@ -2361,20 +2400,20 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1300</v>
       </c>
       <c r="AC22" s="3">
         <v>1300</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
+      <c r="AD22" s="3">
+        <v>1300</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>8</v>
@@ -2391,8 +2430,8 @@
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
@@ -2412,252 +2451,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>135700</v>
+      </c>
+      <c r="E23" s="3">
         <v>137500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>135600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>108300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>96200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>84500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>141500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>159600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>80200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>72700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>52400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>104800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>396200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>50700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>99700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>56400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>52300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>47200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>39400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>39600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-90900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-120900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-203100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-421800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-197500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>174700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>120500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>106600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>290400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>189900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>96900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>42300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>142700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>155300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>93200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>93800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>178400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>122200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E24" s="3">
         <v>35400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>35800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>109600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-21000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-17300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-54500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-97400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>51000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>68300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-9100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>57800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>42100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>27800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>23600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>52900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2778,252 +2826,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E26" s="3">
         <v>102100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>96500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>87200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>62000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>105700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>122300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>58100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>53000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>108300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>286700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>38000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>75400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>40500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>60400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>28800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-89800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-103600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-148600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-324400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-198300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>145900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>85400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>83100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>30200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>239400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>121600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>72700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>51400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>84900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>113200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>65400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>70200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>125400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E27" s="3">
         <v>102000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>96200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>87100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>71800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>61900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>105600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>122400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>58100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>53400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>205400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>338500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>56000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>38500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>75800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>40300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>61500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-89700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-103400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-148200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-324500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-198600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>145800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>85600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>83000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>30300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>239400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>121500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>51300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>84800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>113100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>65300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>70200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>125300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3144,8 +3201,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3180,20 +3240,20 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>97100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>51900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>41800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>35700</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3203,57 +3263,57 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>-26100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>3800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>12100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>22200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>68100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-900</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>11300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>54000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-23700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>207500</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3266,8 +3326,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3388,8 +3451,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3510,8 +3576,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3554,208 +3623,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>100900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>98600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>91500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>89700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>93100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>93000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-26200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>96300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>107900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>92900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>98500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>78300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>85600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>82300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>84200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>82900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>92500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>89800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>94100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>76300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>62600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>61500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>97600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>65700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E33" s="3">
         <v>102000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>96200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>87100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>71800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>61900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>105600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>122400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>58100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>53400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>205400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>338500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>56000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>75800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>40300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-77600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-81200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-148600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-256400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-202300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>145800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>85600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>83000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>29400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>250700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>175500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>27600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>292300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>113100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>65300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>70200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>125300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3876,257 +3951,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E35" s="3">
         <v>102000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>96200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>87100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>71800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>61900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>105600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>122400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>58100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>53400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>205400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>338500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>56000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>75800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>40300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-77600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-81200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-148600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-256400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-202300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>145800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>85600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>83000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>29400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>250700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>175500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>27600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>292300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>113100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>65300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>70200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>125300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46024</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45933</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44925</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44652</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44288</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44197</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44106</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43917</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43826</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43644</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43553</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43462</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43371</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43189</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43098</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43007</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42734</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4169,8 +4253,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4213,175 +4298,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>499400</v>
+      </c>
+      <c r="E41" s="3">
         <v>475700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>439600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>639100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>501500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>920500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>484100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>672500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>436100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>356600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>295600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1927100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>402400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>302700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>305100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>329500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>438900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>429300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>415500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>532600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>483400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1400000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1166200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2509200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2417300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1203000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>264600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>246600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>220100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>195400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>249900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>215000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>185500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>185700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>238800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>154700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>145500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>147000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E42" s="3">
         <v>7900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>43700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>43300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>44900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>42300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>131300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>136000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>111700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>110700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>109800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>109100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4457,252 +4546,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2582700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2475100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2496100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2237200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2357500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2231500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2201100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2100800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2199900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2220600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2198800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1981000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2405900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2353600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2299800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2148000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2052200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1989000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1896700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1748600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1532900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1466100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1511100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1431200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1423200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1851000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1971900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1807000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1832900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1878200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1880300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1790400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1851900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1875200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1813300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1616000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1532900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1508000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1492300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1476300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>433600</v>
+      </c>
+      <c r="E44" s="3">
         <v>453300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>414600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>418800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>394200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>405900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>366700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>387600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>370400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>388300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>367600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>403700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>593200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>609600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>569800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>552400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>514900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>435600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>393300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>412700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>402900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>424500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>427200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>436500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>426800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>403800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>397900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>411300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>393100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>400300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>371100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>724800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>705400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>718200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>614900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>610700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>567600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>571600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>563900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>587200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4736,262 +4834,268 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>620900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>260500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>262200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>192000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>219200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>205200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>205000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>201700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>215900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>311600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>298900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>289900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>198600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>194400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>193500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>196000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>156800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>148700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>171200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>186800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>197400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>198400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>187600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>209300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>169500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>170400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>276500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3855900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3746100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3633600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3522900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3528500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3839800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3294800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3406600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3330400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3328400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3167400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5220000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3725900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3596600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3435100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3292000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3198000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3073100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2910700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2898900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2620900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3506500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3416100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4675800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4557100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3656300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2828900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2658400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2642100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2630600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2650000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2901400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2910100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2976300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2812300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2653100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2464400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2394600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2373600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2492600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E47" s="3">
         <v>157200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>138600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>152700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>188600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>186400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>181900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>162500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>243100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>241400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>251500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>305000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>323500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>539800</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5067,252 +5171,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2584500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2611800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2564800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2436300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2408900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2349300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2279700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2211900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2122300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2122900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2088400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1998200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2682300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2661500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2644900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2624200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2617100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2591600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2589500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2626200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2567400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2552300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2592400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2602300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2617400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2709000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2720000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2181800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2143800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2142900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2153200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1378100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1321400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1356600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1035200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1042000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>981500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1004600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>997600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1023100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6918300</v>
+      </c>
+      <c r="E49" s="3">
         <v>6888800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6770300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6898100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6752600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6709600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6539800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6626700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6443400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6456100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6485500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6580200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7676300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7673800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7644300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7628900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7701900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7532000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7557000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7515900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7558900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7274000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7303800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7276500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7283100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7305700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7550800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7552400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7590900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7610200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7605500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7747400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7776800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7795000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7154600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5836300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5823900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5748700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5692600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5740800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5433,8 +5546,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5555,130 +5671,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>440400</v>
+      </c>
+      <c r="E52" s="3">
         <v>436700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>435500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>180500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>405000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>404300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>410500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>150500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>409500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>412100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>426600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2641300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>989600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>984400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1566200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1537400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1471700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1465500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1408300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1335100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1302900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1154800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1193900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1158100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1164500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1176400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1173300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1343800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1352700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1327100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1330300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1693200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1657300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1604800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1524700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1474700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1380500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1347500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1320200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1325700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5799,130 +5921,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13973900</v>
+      </c>
+      <c r="E54" s="3">
         <v>13840700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13542900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13304600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13283700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13489400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12706700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12674400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12548700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12560900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12419400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16871200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15397500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15456100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15290500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15082400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14988800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14662200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14465500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14376200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14050100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14487700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14506200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15712700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15622100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14847500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>14273100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13736300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13729500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13710800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13738900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13720100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>13665500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>13732800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12526800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11006200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10650400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10495300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10383900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10582100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5965,8 +6093,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6009,740 +6138,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1139100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1246400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1279900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1522700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1137900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1135300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1104800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1394000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1041800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1096600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1096200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1271900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1048600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1137900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1092600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1322900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>908100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>928800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>785400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>919100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>675600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>684900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>644300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>663500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>618100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>785900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>855200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>999500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>819900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>911800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>866200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1018900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>846700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>840400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>833400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>955900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>728900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>803900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>702800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E58" s="3">
         <v>99200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>98800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>92300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>101700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>480700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>996700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1018400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>994200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>92500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>91700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1594300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>180600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>179600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>102700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>65000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>77500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>66600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>52900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>58900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>74100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>80800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>98300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>99900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>90100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>103400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>83000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>69900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>53700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>56300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>53400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>30900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>82000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>72500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>71200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>78200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>74200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>79600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>47600</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>206200</v>
+      </c>
+      <c r="E59" s="3">
         <v>258200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>187300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>987300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>902300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>124200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>242700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>156500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1288900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>142200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>260300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1488900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1897900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1574300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1704200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1533000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1879500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1592500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1631500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1534000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1584100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1411100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1408600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1359300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1635900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1285700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1343000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1277700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1440300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1213900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1385200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1108000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1334000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1098800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1168400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1028800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1291100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3001200</v>
+      </c>
+      <c r="E60" s="3">
         <v>3089700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2855600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3546700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2738000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3183500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3496900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4214200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3453000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2658100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2489400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5030000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2876000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2968100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2684200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3285900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2559900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2699600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2371200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2857400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2342200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2397200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2276600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2347500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2119300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2297900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2297500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2705300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2159400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2311100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2197300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2490200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2142600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2298100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2012600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2368100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1901900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2051900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1779200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2184700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6365500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6325000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6479600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5633700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6516100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6363000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5224200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4548200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5277600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6120100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6174600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5344500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7840100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8216600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8056300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7345900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8084800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7727100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7981600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7393400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7591800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8105600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8111100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9178500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9169500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7862600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7087700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6612200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7198900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7134300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7323700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7213100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7788300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7749500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6976500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5190300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5440100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5214800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5364900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5223500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>653200</v>
+      </c>
+      <c r="E62" s="3">
         <v>619800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>545300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>541900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>559600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>527300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>497300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>479900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>490200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>493900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2355300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>1398500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1412200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1419600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1322400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1319100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1393400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1420100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1351600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1431500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1440700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1427600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1507400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1426300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1088800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1075200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1021700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1000100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>987300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>888800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>889600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>815400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>988700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>985600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>988000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1001300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1012800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6863,8 +7011,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6985,8 +7136,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7107,130 +7261,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10509800</v>
+      </c>
+      <c r="E66" s="3">
         <v>10498500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10309000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10142400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10185500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10455600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9615000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9627900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9597100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9662000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9564700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13150300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11838100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12264700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12147300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12052800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12073500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11758000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11681100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11653300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11363900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11864100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11829100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12976700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12726700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11678100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10821500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10416300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10443600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10477100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10521000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>10690500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>10819800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10937100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9804400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8547200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>8327600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8254600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8145400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>8421100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7273,8 +7433,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7395,8 +7556,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7517,8 +7681,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7639,8 +7806,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7761,130 +7931,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>652300</v>
+      </c>
+      <c r="E72" s="3">
         <v>586300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>515800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>453300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>393700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>349500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>315500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>239700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>144000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>110900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>79300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>964200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>787400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>477600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>450200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>406800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>359300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>347300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>339800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>327600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>320200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>315700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>421200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>532400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>708800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>993000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1223100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1107000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1048600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>992700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>990400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>710500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>560900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>514100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>512300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>247100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>159200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>119700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>74700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8005,8 +8181,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8127,8 +8306,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8249,130 +8431,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3394200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3280300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3208100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3148100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3084100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3020100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3081900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3039000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2943900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2891100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2846600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3712700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3551300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3183300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3143300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3029600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2915300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2904200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2784500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2722900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2686200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2623500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2677100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2736000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2895300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3169400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3451600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3320000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3285900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3233700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3217900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3029600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2845800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2795600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2722400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2459100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2322800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2240700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2238500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2161000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8493,257 +8681,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46024</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45933</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44925</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44652</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44288</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44197</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44106</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43917</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43826</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43644</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43553</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43462</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43371</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43189</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43098</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43007</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42734</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E81" s="3">
         <v>102000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>96200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>87100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>71800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>61900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>105600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>122400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>58100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>53400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>205400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>338500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>56000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>75800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>40300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-77600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-81200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-148600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-256400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-202300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>145800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>85600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>83000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>29400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>250700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>175500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>27600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>292300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>113100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>65300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>70200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>125300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8786,130 +8983,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E83" s="3">
         <v>87100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>84700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>84500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>80600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>81700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>81600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>80000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>80900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>103900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>106300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>106800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>136500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>131500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>133000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>132300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>135500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>138600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>136200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>137300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>138600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>151200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>148100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>148000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>147900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>145200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>148800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>147900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>150700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>152500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>156900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>152900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>133800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>130000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>126400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>125300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>126500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>125600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9030,8 +9231,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9152,8 +9356,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9274,8 +9481,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9396,8 +9606,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9518,130 +9731,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E89" s="3">
         <v>400300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-782200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1175600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>76700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>255900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-587200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1021600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>140700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>221300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-657100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1036500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>314500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-607200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>836500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>375100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-503400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>423300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>337000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-115200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>251500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>16800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>217900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-309500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>776000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>119200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>292600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-203700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>901800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>121300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>335600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-311400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>604200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>21000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>454200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-26000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9684,130 +9903,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-112400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-101300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-122200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-142200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-111400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-115800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-119900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-139300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-85100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-87400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-115600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-125000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-88000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-81700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-88900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-128300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-87100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-99300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-73700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-153500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-106000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-79100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-69200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-119800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-85100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-114400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-99200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-162600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-110000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-116000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-114400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-195800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-184400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-129500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-118900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-212400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-125200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-108500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-106600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-324700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9928,8 +10151,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10050,130 +10276,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-119300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-162800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-153700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-108200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-131700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-251600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-230800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-89600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-91900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-198000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-73000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>507800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-141700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-84100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-189800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-351600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-112200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-177700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-131200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-327500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-84900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-90800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-109800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-54700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-109200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-87400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-160100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-107600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-136000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>194200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-193100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-195900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1033500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1442800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-224700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-177800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-169900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-106100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-295400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10216,43 +10448,44 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>31500</v>
+        <v>31600</v>
       </c>
       <c r="E96" s="3">
         <v>31500</v>
       </c>
       <c r="F96" s="3">
+        <v>31500</v>
+      </c>
+      <c r="G96" s="3">
         <v>27600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>27500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>27800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>27900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>25000</v>
       </c>
       <c r="K96" s="3">
         <v>25000</v>
       </c>
       <c r="L96" s="3">
-        <v>24900</v>
+        <v>25000</v>
       </c>
       <c r="M96" s="3">
         <v>24900</v>
       </c>
       <c r="N96" s="3">
-        <v>28700</v>
+        <v>24900</v>
       </c>
       <c r="O96" s="3">
         <v>28700</v>
@@ -10261,34 +10494,34 @@
         <v>28700</v>
       </c>
       <c r="Q96" s="3">
+        <v>28700</v>
+      </c>
+      <c r="R96" s="3">
         <v>-28600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-28400</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-28300</v>
       </c>
       <c r="T96" s="3">
         <v>-28300</v>
       </c>
       <c r="U96" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="V96" s="3">
         <v>-28200</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-28100</v>
       </c>
       <c r="W96" s="3">
         <v>-28100</v>
       </c>
       <c r="X96" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-27900</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-27800</v>
       </c>
       <c r="AA96" s="3">
         <v>-27800</v>
@@ -10297,10 +10530,10 @@
         <v>-27800</v>
       </c>
       <c r="AC96" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-27500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-27100</v>
       </c>
       <c r="AE96" s="3">
         <v>-27100</v>
@@ -10309,10 +10542,10 @@
         <v>-27100</v>
       </c>
       <c r="AG96" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-27200</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-25800</v>
       </c>
       <c r="AI96" s="3">
         <v>-25800</v>
@@ -10324,22 +10557,25 @@
         <v>-25800</v>
       </c>
       <c r="AL96" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-25300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-25200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-25100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-25200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-23200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10460,8 +10696,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10582,8 +10821,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10704,231 +10946,237 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-203200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>735700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-914000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-387200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>423900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>642700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-760600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>32400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-54000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-779000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>606200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-416900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-183400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>657100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-741200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>385700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-247100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>565000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-238400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-603300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1148200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-58700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1251000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>833700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>411600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-584200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>12700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-211500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>48100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-663800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>59100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>697700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1701100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-295400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>166000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-285800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>126500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-190200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E101" s="3">
         <v>7500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-19000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>11700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>11700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-10800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
+      <c r="AJ101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK101" s="3">
         <v>0</v>
@@ -10948,126 +11196,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E102" s="3">
         <v>32500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-198800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>149400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-416300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>435600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-194300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>237100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>81400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>70500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1628700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1561200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>112300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-22600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-109400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-117100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>49200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-916600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>233800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1343000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>91900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1214300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>938300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>26600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>24700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-54500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>34900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>49100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-19600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-53100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>84100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>9200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-5600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-43900</v>
       </c>
     </row>
